--- a/static/templates_importacao/2_diarias.xlsx
+++ b/static/templates_importacao/2_diarias.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diárias" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diárias - SIGE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="13"/>
     </font>
     <font>
       <i val="1"/>
@@ -36,16 +36,30 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00155724"/>
+      <b val="1"/>
+      <color rgb="00777777"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -54,27 +68,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00155724"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001e7e34"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00e8f5e9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00d4edda"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00fff3cd"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,38 +122,68 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,135 +550,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Template Diárias — Formato SIGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Valores (diária, VA, VT) são obtidos automaticamente do cadastro do funcionário · Obras buscadas por nome parcial · Tipos especiais no campo Obra (veja exemplos abaixo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>nome_funcionario</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>obra</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Funcionário *</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Data *</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Obra</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Nome exato do funcionário cadastrado</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>DD/MM/AAAA</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Nome ou código da obra (opcional)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE ou APROVADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Obra / Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>João da Silva</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>15/04/2025</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Obra Central</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Maria Souza</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>15/04/2025</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>FERIADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Pedro Alves</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2025</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>FOLGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>João da Silva</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>16/04/2025</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>FALTOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Maria Souza</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>17/04/2025</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>ATESTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Alves</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>17/04/2025</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Reforma Norte</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ATENÇÃO: Os valores (diária, VA e VT) são obtidos automaticamente do cadastro do funcionário.</t>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2025</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>FALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Tipos especiais no campo Obra / Tipo:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>FERIADO / FALTOU / DESCANSO / FOLGA / FALTA</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Sem lançamento de custo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>ATESTADO</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Lança só a diária (sem VA e VT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Qualquer outro valor</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Lança diária + VA + VT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A7:D7"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
